--- a/Dynamics BC Excel Reports/ReportLayouts/Excel/GeneralLedger/TrialBalanceExcel.xlsx
+++ b/Dynamics BC Excel Reports/ReportLayouts/Excel/GeneralLedger/TrialBalanceExcel.xlsx
@@ -1,127 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <x:workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws\20250818\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4DE844-13E0-47E5-BA23-4F911FC5ECB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="28695" yWindow="-24000" windowWidth="29010" windowHeight="23385" tabRatio="941" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="$TrialBalancePrint$" sheetId="17" r:id="rId1"/>
-    <sheet name="$TrialBalanceLCYAnalysis$" sheetId="20" r:id="rId2"/>
-    <sheet name="$TrialBalanceACYSheetAnalysis$" sheetId="21" r:id="rId3"/>
-    <sheet name="$AboutTheReportLabel$" sheetId="13" r:id="rId4"/>
-    <sheet name="TranslationData" sheetId="2" state="hidden" r:id="rId5"/>
-    <sheet name="CaptionData" sheetId="3" state="hidden" r:id="rId6"/>
-    <sheet name="Metadata" sheetId="11" state="hidden" r:id="rId7"/>
-    <sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId8"/>
-    <sheet name="GLAccounts" sheetId="5" state="hidden" r:id="rId9"/>
-    <sheet name="Dimension1" sheetId="6" state="hidden" r:id="rId10"/>
-    <sheet name="Dimension2" sheetId="7" state="hidden" r:id="rId11"/>
-    <sheet name="TrialBalanceData" sheetId="8" state="hidden" r:id="rId12"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_NewTemplate.xlsxDimension11" hidden="1">Dimension1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_NewTemplate.xlsxDimension21" hidden="1">Dimension2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_NewTemplate.xlsxGLAccounts1" hidden="1">GLAccounts[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_NewTemplate.xlsxTrialBalanceData1" hidden="1">TrialBalanceData[]</definedName>
-    <definedName name="CompanyName">Metadata!$A$1</definedName>
-    <definedName name="DataRetrieved">Metadata!$A$3</definedName>
-    <definedName name="Date">Metadata!$A$2</definedName>
-    <definedName name="DateFilter">_xlfn.XLOOKUP("DateFilter", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" localSheetId="2">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" localSheetId="1">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" localSheetId="0">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" localSheetId="2">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" localSheetId="1">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" localSheetId="0">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="Slicer_AccountCategory2">#N/A</definedName>
-    <definedName name="Slicer_AccountCategory21">#N/A</definedName>
-    <definedName name="Slicer_AccountSubcategory2">#N/A</definedName>
-    <definedName name="Slicer_AccountSubcategory21">#N/A</definedName>
-    <definedName name="Slicer_Dimension1.Dim1Code">#N/A</definedName>
-    <definedName name="Slicer_Dimension1.Dim1Code1">#N/A</definedName>
-    <definedName name="Slicer_Dimension2.Dim2Code">#N/A</definedName>
-    <definedName name="Slicer_Dimension2.Dim2Code1">#N/A</definedName>
-  </definedNames>
-  <calcPr calcId="191029" forceFullCalc="1"/>
-  <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId13"/>
-  </pivotCaches>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+  <x:bookViews>
+    <x:workbookView xWindow="28695" yWindow="-24000" windowWidth="29010" windowHeight="23385" tabRatio="941" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="$TrialBalancePrint$" sheetId="17" r:id="rId1"/>
+    <x:sheet name="$TrialBalanceLCYAnalysis$" sheetId="20" r:id="rId2"/>
+    <x:sheet name="$TrialBalanceACYSheetAnalysis$" sheetId="21" r:id="rId3"/>
+    <x:sheet name="$AboutTheReportLabel$" sheetId="13" r:id="rId4"/>
+    <x:sheet name="TranslationData" sheetId="2" state="hidden" r:id="rId5"/>
+    <x:sheet name="CaptionData" sheetId="3" state="hidden" r:id="rId6"/>
+    <x:sheet name="Metadata" sheetId="11" state="hidden" r:id="rId7"/>
+    <x:sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId8"/>
+    <x:sheet name="GLAccounts" sheetId="5" state="hidden" r:id="rId9"/>
+    <x:sheet name="Dimension1" sheetId="6" state="hidden" r:id="rId10"/>
+    <x:sheet name="Dimension2" sheetId="7" state="hidden" r:id="rId11"/>
+    <x:sheet name="TrialBalanceData" sheetId="8" state="hidden" r:id="rId12"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="_xlcn.WorksheetConnection_NewTemplate.xlsxDimension11" hidden="1">Dimension1[]</x:definedName>
+    <x:definedName name="_xlcn.WorksheetConnection_NewTemplate.xlsxDimension21" hidden="1">Dimension2[]</x:definedName>
+    <x:definedName name="_xlcn.WorksheetConnection_NewTemplate.xlsxGLAccounts1" hidden="1">GLAccounts[]</x:definedName>
+    <x:definedName name="_xlcn.WorksheetConnection_NewTemplate.xlsxTrialBalanceData1" hidden="1">TrialBalanceData[]</x:definedName>
+    <x:definedName name="CompanyName">Metadata!$A$1</x:definedName>
+    <x:definedName name="DataRetrieved">Metadata!$A$3</x:definedName>
+    <x:definedName name="Date">Metadata!$A$2</x:definedName>
+    <x:definedName name="DateFilter">_xlfn.XLOOKUP("DateFilter", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" localSheetId="2">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" localSheetId="1">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" localSheetId="0">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" localSheetId="2">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" localSheetId="1">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" localSheetId="0">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet" localSheetId="0">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="Slicer_AccountCategory2">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountCategory21">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountSubcategory2">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountSubcategory21">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension1.Dim1Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension1.Dim1Code1">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension2.Dim2Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension2.Dim2Code1">#N/A</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029" forceFullCalc="1"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="8" r:id="rId13"/>
+  </x:pivotCaches>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId14"/>
         <x14:slicerCache r:id="rId15"/>
@@ -132,11 +132,11 @@
         <x14:slicerCache r:id="rId20"/>
         <x14:slicerCache r:id="rId21"/>
       </x14:slicerCaches>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+    </x:ext>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
+    </x:ext>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
       <x15:dataModel>
         <x15:modelTables>
           <x15:modelTable id="MergedQuery  2_23f92ba7-c7ca-4dae-8c68-8ba597ed01f0" name="MergedQuery  2" connection="Query - MergedQuery (2)"/>
@@ -151,8 +151,8 @@
           <x15:modelRelationship fromTable="TrialBalanceData" fromColumn="Dimension2Code" toTable="Dimension2" toColumn="Dim2Code"/>
         </x15:modelRelationships>
       </x15:dataModel>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    </x:ext>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -162,9 +162,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7151,33 +7151,33 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="TrialBalanceData" displayName="TrialBalanceData" ref="A1:U2" totalsRowShown="0" headerRowDxfId="778">
-  <autoFilter ref="A1:U2" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
-  <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Account"/>
-    <tableColumn id="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dimension1Code"/>
-    <tableColumn id="3" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dimension2Code"/>
-    <tableColumn id="18" xr3:uid="{77CD2FBC-13C2-455B-B0B8-8EE92A92A255}" name="StartingBalance" dataDxfId="772"/>
-    <tableColumn id="19" xr3:uid="{C10F5B79-1213-4DA3-AE14-2400B91FB70E}" name="StartingBalanceDebit" dataDxfId="773"/>
-    <tableColumn id="17" xr3:uid="{23504BCC-E3F0-4B2F-93AD-44DB4567C77E}" name="StartingBalanceCredit" dataDxfId="774"/>
-    <tableColumn id="4" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChange"/>
-    <tableColumn id="5" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeDebit"/>
-    <tableColumn id="6" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeCredit"/>
-    <tableColumn id="7" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Balance"/>
-    <tableColumn id="8" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceDebit"/>
-    <tableColumn id="9" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceCredit"/>
-    <tableColumn id="22" xr3:uid="{5D58A870-5310-49FE-8817-26ECBA489E9A}" name="StartingBalanceACY" dataDxfId="775"/>
-    <tableColumn id="21" xr3:uid="{46A7DA7F-EF8C-428F-9466-D0C8787D2A91}" name="StartingBalanceDebitACY" dataDxfId="776"/>
-    <tableColumn id="20" xr3:uid="{EA02974A-7C20-41AE-89E2-63F6A77054B7}" name="StartingBalanceCreditACY" dataDxfId="777"/>
-    <tableColumn id="10" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeACY"/>
-    <tableColumn id="11" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeDebitACY"/>
-    <tableColumn id="12" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="NetChangeCreditACY"/>
-    <tableColumn id="13" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceACY"/>
-    <tableColumn id="14" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceDebitACY"/>
-    <tableColumn id="15" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="BalanceCreditACY"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TrialBalanceData" displayName="TrialBalanceData" ref="A1:U2" totalsRowShown="0" headerRowDxfId="778" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:U2" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
+  <x:tableColumns count="21">
+    <x:tableColumn id="1" name="Account" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="2" name="Dimension1Code" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="3" name="Dimension2Code" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="18" name="StartingBalance" dataDxfId="772" xr3:uid="{77CD2FBC-13C2-455B-B0B8-8EE92A92A255}"/>
+    <x:tableColumn id="19" name="StartingBalanceDebit" dataDxfId="773" xr3:uid="{C10F5B79-1213-4DA3-AE14-2400B91FB70E}"/>
+    <x:tableColumn id="17" name="StartingBalanceCredit" dataDxfId="774" xr3:uid="{23504BCC-E3F0-4B2F-93AD-44DB4567C77E}"/>
+    <x:tableColumn id="4" name="NetChange" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="5" name="NetChangeDebit" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="6" name="NetChangeCredit" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="7" name="Balance" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="8" name="BalanceDebit" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="9" name="BalanceCredit" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="22" name="StartingBalanceACY" dataDxfId="775" xr3:uid="{5D58A870-5310-49FE-8817-26ECBA489E9A}"/>
+    <x:tableColumn id="21" name="StartingBalanceDebitACY" dataDxfId="776" xr3:uid="{46A7DA7F-EF8C-428F-9466-D0C8787D2A91}"/>
+    <x:tableColumn id="20" name="StartingBalanceCreditACY" dataDxfId="777" xr3:uid="{EA02974A-7C20-41AE-89E2-63F6A77054B7}"/>
+    <x:tableColumn id="10" name="NetChangeACY" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="11" name="NetChangeDebitACY" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="12" name="NetChangeCreditACY" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="13" name="BalanceACY" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="14" name="BalanceDebitACY" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="15" name="BalanceCreditACY" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7236,42 +7236,42 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="GLAccounts" displayName="GLAccounts" ref="A1:H2" totalsRowShown="0" headerRowDxfId="781">
-  <autoFilter ref="A1:H2" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountNumber"/>
-    <tableColumn id="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountName"/>
-    <tableColumn id="3" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="IncomeBalance"/>
-    <tableColumn id="4" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountCategory"/>
-    <tableColumn id="5" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountSubcategory"/>
-    <tableColumn id="6" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="AccountType"/>
-    <tableColumn id="7" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Indentation"/>
-    <tableColumn id="8" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="IndentedAccountName"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="GLAccounts" displayName="GLAccounts" ref="A1:H2" totalsRowShown="0" headerRowDxfId="781" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:H2" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="AccountNumber" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="2" name="AccountName" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="3" name="IncomeBalance" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="4" name="AccountCategory" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="5" name="AccountSubcategory" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="6" name="AccountType" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="7" name="Indentation" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="8" name="IndentedAccountName" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="Dimension1" displayName="Dimension1" ref="A1:B2" totalsRowShown="0" headerRowDxfId="780">
-  <autoFilter ref="A1:B2" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dim1Code"/>
-    <tableColumn id="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dim1Name"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Dimension1" displayName="Dimension1" ref="A1:B2" totalsRowShown="0" headerRowDxfId="780" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:B2" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
+  <x:tableColumns count="2">
+    <x:tableColumn id="1" name="Dim1Code" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="2" name="Dim1Name" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="Dimension2" displayName="Dimension2" ref="A1:B2" totalsRowShown="0" headerRowDxfId="779">
-  <autoFilter ref="A1:B2" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dim2Code"/>
-    <tableColumn id="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Dim2Name"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Dimension2" displayName="Dimension2" ref="A1:B2" totalsRowShown="0" headerRowDxfId="779" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:B2" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
+  <x:tableColumns count="2">
+    <x:tableColumn id="1" name="Dim2Code" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="2" name="Dim2Name" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
